--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1073,7 +1073,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,9 +256,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -659,13 +659,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1618: source value from ELECTROCARDIOGRAM (EKG) - IEN (#691.5-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1618: source value from ELECTROCARDIOGRAM (EKG) - IEN (#691.5-.001)</t>
   </si>
   <si>
     <t>Observation.identifier.period</t>
@@ -791,6 +791,9 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImageStatus</t>
   </si>
   <si>
+    <t>1622: terminologyMaps using VF_ImageStatus on ELECTROCARDIOGRAM (EKG) - RELEASE STATUS (#691.5-1506)</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -804,9 +807,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1622: terminologyMaps using VF_ImageStatus on ELECTROCARDIOGRAM (EKG) - RELEASE STATUS (#691.5-1506)</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -913,6 +913,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>1632: reference from ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (#691.5-1)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -923,9 +926,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1632: reference from ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (#691.5-1)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1058,6 +1058,9 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>1638: source value from ELECTROCARDIOGRAM (EKG) - DATE OF VERIFIED (#691.5-1508)</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1065,9 +1068,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>1638: source value from ELECTROCARDIOGRAM (EKG) - DATE OF VERIFIED (#691.5-1508)</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1086,6 +1086,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1641: reference from ELECTROCARDIOGRAM (EKG) - INTERPRETED BY (#691.5-12)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1096,9 +1099,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1641: reference from ELECTROCARDIOGRAM (EKG) - INTERPRETED BY (#691.5-12)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1200,6 +1200,9 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImageInterpretation</t>
   </si>
   <si>
+    <t>1649: terminologyMaps using VF_ImageInterpretation on ELECTROCARDIOGRAM (EKG) - SUMMARY (#691.5-.03)</t>
+  </si>
+  <si>
     <t>&lt; 260245000 |Findings values|</t>
   </si>
   <si>
@@ -1210,9 +1213,6 @@
   </si>
   <si>
     <t>363713009 |Has interpretation|</t>
-  </si>
-  <si>
-    <t>1649: terminologyMaps using VF_ImageInterpretation on ELECTROCARDIOGRAM (EKG) - SUMMARY (#691.5-.03)</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1234,13 +1234,13 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
+    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (#691.5-.03)</t>
+  </si>
+  <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
     <t>subjectOf.observationEvent[code="annotation"].value</t>
-  </si>
-  <si>
-    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (#691.5-.03)</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2024,13 +2024,13 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="228.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="228.015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2266,19 +2266,19 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>83</v>
@@ -2888,10 +2888,10 @@
         <v>83</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>83</v>
@@ -3011,10 +3011,10 @@
         <v>83</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>83</v>
@@ -3134,10 +3134,10 @@
         <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>83</v>
@@ -3259,10 +3259,10 @@
         <v>83</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>83</v>
@@ -3373,22 +3373,22 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>83</v>
@@ -3503,10 +3503,10 @@
         <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>83</v>
@@ -3626,10 +3626,10 @@
         <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -3748,13 +3748,13 @@
         <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>83</v>
@@ -3873,13 +3873,13 @@
         <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3998,13 +3998,13 @@
         <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4115,25 +4115,25 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4242,13 +4242,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4365,13 +4365,13 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4482,19 +4482,19 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4605,19 +4605,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4743,10 +4743,10 @@
         <v>253</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>83</v>
+        <v>254</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>254</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4860,13 +4860,13 @@
         <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4987,13 +4987,13 @@
         <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5101,25 +5101,25 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5229,10 +5229,10 @@
         <v>287</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>289</v>
@@ -5241,10 +5241,10 @@
         <v>290</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5355,16 +5355,16 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AP27" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5474,22 +5474,22 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5597,22 +5597,22 @@
         <v>318</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5724,25 +5724,25 @@
         <v>318</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AP30" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ30" t="s" s="2">
-        <v>326</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5847,13 +5847,13 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>333</v>
@@ -5862,10 +5862,10 @@
         <v>334</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5973,10 +5973,10 @@
         <v>341</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>83</v>
+        <v>342</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>343</v>
@@ -5985,10 +5985,10 @@
         <v>344</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -6096,22 +6096,22 @@
         <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6220,25 +6220,25 @@
         <v>353</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6351,13 +6351,13 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6468,10 +6468,10 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>378</v>
@@ -6480,10 +6480,10 @@
         <v>379</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>381</v>
@@ -6593,25 +6593,25 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>389</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6719,22 +6719,22 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6847,13 +6847,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6967,22 +6967,22 @@
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7090,22 +7090,22 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7218,13 +7218,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7342,10 +7342,10 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7465,10 +7465,10 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7590,10 +7590,10 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7708,13 +7708,13 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7829,13 +7829,13 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7951,16 +7951,16 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="AO48" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8076,16 +8076,16 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="AO49" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8205,10 +8205,10 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8323,13 +8323,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8446,13 +8446,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8569,13 +8569,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8694,13 +8694,13 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8818,10 +8818,10 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -8941,10 +8941,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9066,10 +9066,10 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9185,19 +9185,19 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9310,22 +9310,22 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9438,13 +9438,13 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -9560,7 +9560,7 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>378</v>
@@ -9569,13 +9569,13 @@
         <v>379</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9688,13 +9688,13 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="528">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -822,28 +822,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -852,6 +830,31 @@
     &lt;code value="imaging"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -4799,7 +4802,7 @@
         <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>83</v>
@@ -4817,16 +4820,16 @@
         <v>117</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4851,7 +4854,7 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
@@ -4863,10 +4866,10 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4874,13 +4877,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>255</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -4924,7 +4927,7 @@
         <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>83</v>
@@ -4942,10 +4945,10 @@
         <v>117</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4990,10 +4993,10 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5001,14 +5004,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5030,16 +5033,16 @@
         <v>182</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5068,7 +5071,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5086,7 +5089,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>93</v>
@@ -5104,30 +5107,30 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5150,19 +5153,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5211,7 +5214,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5226,22 +5229,22 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5249,10 +5252,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5275,16 +5278,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5334,7 +5337,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5358,13 +5361,13 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5372,14 +5375,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5398,19 +5401,19 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5459,7 +5462,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5477,19 +5480,19 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5497,14 +5500,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5523,19 +5526,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5572,7 +5575,7 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5582,7 +5585,7 @@
         <v>169</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5591,28 +5594,28 @@
         <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5620,16 +5623,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5648,19 +5651,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5709,7 +5712,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5718,28 +5721,28 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5747,10 +5750,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5773,16 +5776,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5832,7 +5835,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5847,7 +5850,7 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
@@ -5856,13 +5859,13 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5870,10 +5873,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5896,17 +5899,17 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5955,7 +5958,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5970,22 +5973,22 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -5993,10 +5996,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6019,19 +6022,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6068,7 +6071,7 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6078,7 +6081,7 @@
         <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6087,10 +6090,10 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6099,30 +6102,30 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>83</v>
@@ -6147,16 +6150,16 @@
         <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6205,7 +6208,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6214,39 +6217,39 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6272,16 +6275,16 @@
         <v>182</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6309,10 +6312,10 @@
         <v>187</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6330,7 +6333,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6339,7 +6342,7 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6357,7 +6360,7 @@
         <v>136</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6368,14 +6371,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6397,16 +6400,16 @@
         <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6435,7 +6438,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6453,7 +6456,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6468,33 +6471,33 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6517,19 +6520,19 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6578,7 +6581,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6593,7 +6596,7 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
@@ -6602,10 +6605,10 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6616,10 +6619,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6645,13 +6648,13 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6677,13 +6680,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6701,7 +6704,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6722,27 +6725,27 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6768,16 +6771,16 @@
         <v>182</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6802,13 +6805,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6826,7 +6829,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6850,10 +6853,10 @@
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6864,10 +6867,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6890,16 +6893,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6949,7 +6952,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6970,27 +6973,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7013,16 +7016,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7072,7 +7075,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7093,27 +7096,27 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7136,19 +7139,19 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7197,7 +7200,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7209,7 +7212,7 @@
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7221,10 +7224,10 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7235,10 +7238,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7356,10 +7359,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7479,14 +7482,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7508,10 +7511,10 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>142</v>
@@ -7566,7 +7569,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7604,10 +7607,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7630,13 +7633,13 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7687,7 +7690,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7696,7 +7699,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -7711,10 +7714,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7725,10 +7728,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7751,13 +7754,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7808,7 +7811,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7817,7 +7820,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7832,10 +7835,10 @@
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7846,10 +7849,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7875,16 +7878,16 @@
         <v>182</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7912,10 +7915,10 @@
         <v>117</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7933,7 +7936,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7954,13 +7957,13 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -7971,10 +7974,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8000,16 +8003,16 @@
         <v>182</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8034,13 +8037,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8058,7 +8061,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8079,13 +8082,13 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8096,10 +8099,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8122,17 +8125,17 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8181,7 +8184,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8208,7 +8211,7 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8219,10 +8222,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8248,10 +8251,10 @@
         <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8302,7 +8305,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8326,10 +8329,10 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8340,10 +8343,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8366,16 +8369,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8425,7 +8428,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8449,10 +8452,10 @@
         <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8463,10 +8466,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8489,16 +8492,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8548,7 +8551,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8572,10 +8575,10 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8586,10 +8589,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8612,19 +8615,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8673,7 +8676,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8697,10 +8700,10 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8711,10 +8714,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8832,10 +8835,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8955,14 +8958,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8984,10 +8987,10 @@
         <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>142</v>
@@ -9042,7 +9045,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9080,10 +9083,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9109,16 +9112,16 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9143,13 +9146,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9167,7 +9170,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>93</v>
@@ -9188,16 +9191,16 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9205,10 +9208,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9231,19 +9234,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9292,7 +9295,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9313,27 +9316,27 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9359,16 +9362,16 @@
         <v>182</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9396,10 +9399,10 @@
         <v>187</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9417,7 +9420,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9426,7 +9429,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9444,7 +9447,7 @@
         <v>136</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -9455,14 +9458,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9484,16 +9487,16 @@
         <v>182</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9521,28 +9524,28 @@
         <v>187</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9563,27 +9566,27 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9609,16 +9612,16 @@
         <v>84</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9667,7 +9670,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9691,10 +9694,10 @@
         <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ELECTROCARDIOGRAM (EKG) (#691.5) to us-core-observation-imaging</t>
+    <t>This StructureDefinition contains the maps for VistA file ELECTROCARDIOGRAM (EKG) (691.5) to us-core-observation-imaging</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1618: source value from ELECTROCARDIOGRAM (EKG) - IEN (#691.5-.001)</t>
+    <t>1618: source value from ELECTROCARDIOGRAM (EKG) - IEN (691.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImageStatus</t>
   </si>
   <si>
-    <t>1622: terminologyMaps using VF_ImageStatus on ELECTROCARDIOGRAM (EKG) - RELEASE STATUS (#691.5-1506)</t>
+    <t>1622: terminologyMaps using VF_ImageStatus on ELECTROCARDIOGRAM (EKG) - RELEASE STATUS (691.5-1506)</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -919,7 +919,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1632: reference from ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (#691.5-1)</t>
+    <t>1632: reference from ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (691.5-1)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1045,7 +1045,7 @@
 </t>
   </si>
   <si>
-    <t>1635: source value from ELECTROCARDIOGRAM (EKG) - DATE/TIME (#691.5-.01)</t>
+    <t>1635: source value from ELECTROCARDIOGRAM (EKG) - DATE/TIME (691.5-.01)</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1064,7 +1064,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1638: source value from ELECTROCARDIOGRAM (EKG) - DATE OF VERIFIED (#691.5-1508)</t>
+    <t>1638: source value from ELECTROCARDIOGRAM (EKG) - DATE OF VERIFIED (691.5-1508)</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1092,7 +1092,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1641: reference from ELECTROCARDIOGRAM (EKG) - INTERPRETED BY (#691.5-12)</t>
+    <t>1641: reference from ELECTROCARDIOGRAM (EKG) - INTERPRETED BY (691.5-12)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1152,7 +1152,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1646: source value from ELECTROCARDIOGRAM (EKG) - INTERPRETATION CODE (PACING) &gt; INTERPRETATION CODE (PACING) - INTERPRETATION CODE (PACING) &gt; ECG INTERPRETATION - INTERPRETATION (#691.5-14.2 &gt; 691.56-.01 &gt; 693.3-.01)</t>
+    <t>1646: source value from ELECTROCARDIOGRAM (EKG) - INTERPRETATION CODE (PACING) &gt; INTERPRETATION CODE (PACING) - INTERPRETATION CODE (PACING) &gt; ECG INTERPRETATION - INTERPRETATION (691.5-14.2 &gt; 691.56-.01 &gt; 693.3-.01)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>
@@ -1231,7 +1231,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImageInterpretation</t>
   </si>
   <si>
-    <t>1649: terminologyMaps using VF_ImageInterpretation on ELECTROCARDIOGRAM (EKG) - SUMMARY (#691.5-.03)</t>
+    <t>1649: terminologyMaps using VF_ImageInterpretation on ELECTROCARDIOGRAM (EKG) - SUMMARY (691.5-.03)</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1265,7 +1265,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (#691.5-.03)</t>
+    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (691.5-.03)</t>
   </si>
   <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
@@ -2055,7 +2055,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="228.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="226.4765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1265,7 +1265,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (691.5-.03)</t>
+    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (691.5-17)</t>
   </si>
   <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2623" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2623" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1618-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -3984,7 +3990,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4015,10 +4021,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4054,7 +4060,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4069,7 +4075,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4081,10 +4087,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4095,10 +4101,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4124,13 +4130,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4144,7 +4150,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4180,7 +4186,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4195,7 +4201,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4207,10 +4213,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4221,10 +4227,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4247,13 +4253,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4304,7 +4310,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4331,10 +4337,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4345,10 +4351,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4371,16 +4377,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4430,7 +4436,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4457,10 +4463,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4471,14 +4477,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4497,17 +4503,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4556,7 +4562,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4577,16 +4583,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4597,14 +4603,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4623,16 +4629,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4682,7 +4688,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4703,16 +4709,16 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4723,10 +4729,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4752,16 +4758,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4790,7 +4796,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4808,7 +4814,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -4823,25 +4829,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4849,10 +4855,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4878,16 +4884,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4897,7 +4903,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4915,16 +4921,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4934,7 +4940,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4949,7 +4955,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -4964,10 +4970,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4975,13 +4981,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5006,16 +5012,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5025,7 +5031,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5043,10 +5049,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5064,7 +5070,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5094,10 +5100,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5105,14 +5111,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5134,16 +5140,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5172,7 +5178,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5190,7 +5196,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5211,30 +5217,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5257,19 +5263,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5318,7 +5324,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5333,25 +5339,25 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5359,10 +5365,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5385,16 +5391,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5444,7 +5450,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5471,13 +5477,13 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5485,14 +5491,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5511,19 +5517,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5572,7 +5578,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5593,19 +5599,19 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5613,14 +5619,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5639,19 +5645,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5688,7 +5694,7 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5698,7 +5704,7 @@
         <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5707,10 +5713,10 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5719,19 +5725,19 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5739,16 +5745,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5767,19 +5773,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5828,7 +5834,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5837,31 +5843,31 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5869,10 +5875,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5895,16 +5901,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5954,7 +5960,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5969,7 +5975,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -5981,13 +5987,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -5995,10 +6001,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6021,17 +6027,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6080,7 +6086,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6095,25 +6101,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6121,10 +6127,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6147,19 +6153,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6196,7 +6202,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6206,7 +6212,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6215,10 +6221,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6230,30 +6236,30 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -6278,16 +6284,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6336,7 +6342,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6345,13 +6351,13 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6360,30 +6366,30 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6405,19 +6411,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6466,7 +6472,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6475,13 +6481,13 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>84</v>
@@ -6490,30 +6496,30 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>84</v>
@@ -6538,16 +6544,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6596,7 +6602,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6605,13 +6611,13 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6620,27 +6626,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6666,16 +6672,16 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6703,10 +6709,10 @@
         <v>188</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6724,7 +6730,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6733,13 +6739,13 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
@@ -6754,7 +6760,7 @@
         <v>137</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6765,14 +6771,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6794,16 +6800,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6832,7 +6838,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6850,7 +6856,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6865,7 +6871,7 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>84</v>
@@ -6874,27 +6880,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6917,19 +6923,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6978,7 +6984,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6993,7 +6999,7 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
@@ -7005,10 +7011,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7019,10 +7025,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7048,13 +7054,13 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7080,13 +7086,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7104,7 +7110,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7128,27 +7134,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7174,16 +7180,16 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7208,13 +7214,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7232,7 +7238,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7259,10 +7265,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7273,10 +7279,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7299,16 +7305,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7358,7 +7364,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7382,27 +7388,27 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7425,16 +7431,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7484,7 +7490,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7508,27 +7514,27 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7551,19 +7557,19 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7612,7 +7618,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7624,7 +7630,7 @@
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7639,10 +7645,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7653,10 +7659,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7777,10 +7783,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7903,14 +7909,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7932,10 +7938,10 @@
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -7990,7 +7996,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8031,10 +8037,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8057,13 +8063,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8114,7 +8120,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8123,7 +8129,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8141,10 +8147,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8155,10 +8161,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8181,13 +8187,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8238,7 +8244,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8247,7 +8253,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8265,10 +8271,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8279,10 +8285,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8308,16 +8314,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8345,10 +8351,10 @@
         <v>118</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8366,7 +8372,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8390,13 +8396,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8407,10 +8413,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8436,16 +8442,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8470,13 +8476,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8494,7 +8500,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8518,13 +8524,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8535,10 +8541,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8561,17 +8567,17 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8620,7 +8626,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8650,7 +8656,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8661,10 +8667,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8690,10 +8696,10 @@
         <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8744,7 +8750,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8771,10 +8777,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8785,10 +8791,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8811,16 +8817,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8870,7 +8876,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8897,10 +8903,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8911,10 +8917,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8937,16 +8943,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8996,7 +9002,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9023,10 +9029,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9037,10 +9043,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9063,19 +9069,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9124,7 +9130,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9151,10 +9157,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9165,10 +9171,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9289,10 +9295,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9415,14 +9421,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9444,10 +9450,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9502,7 +9508,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9543,10 +9549,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9572,16 +9578,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9606,13 +9612,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9630,7 +9636,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>94</v>
@@ -9654,16 +9660,16 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>84</v>
@@ -9671,10 +9677,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9697,19 +9703,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9758,7 +9764,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9782,27 +9788,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9828,16 +9834,16 @@
         <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9865,10 +9871,10 @@
         <v>188</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9886,7 +9892,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9895,7 +9901,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9916,7 +9922,7 @@
         <v>137</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9927,14 +9933,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9956,16 +9962,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9993,28 +9999,28 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Z63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10038,27 +10044,27 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10084,16 +10090,16 @@
         <v>85</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10142,7 +10148,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10169,10 +10175,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/691.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1618-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1618-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/691.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/691.5</t>
+    <t>http://va.gov/identifiers/$Sta3n/691.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1618-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/691.5</t>
+    <t>1618-1: fixed value = http://va.gov/identifiers/$Sta3n/691.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1085,7 +1085,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -909,7 +909,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -909,7 +909,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFImageStatus</t>
+    <t>http://va.gov/fhir/ValueSet/ImageStatus</t>
   </si>
   <si>
     <t>1622: terminologyMaps using VF_ImageStatus on ELECTROCARDIOGRAM (EKG) - RELEASE STATUS (691.5-1506)</t>
@@ -1234,7 +1234,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFImageInterpretation</t>
+    <t>http://va.gov/fhir/ValueSet/ImageInterpretation</t>
   </si>
   <si>
     <t>1649: terminologyMaps using VF_ImageInterpretation on ELECTROCARDIOGRAM (EKG) - SUMMARY (691.5-.03)</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ELECTROCARDIOGRAM (EKG) (691.5) to us-core-observation-imaging</t>
+    <t>This StructureDefinition contains the maps for VistA file ELECTROCARDIOGRAM (EKG) (691.5) to us-core-observation-imaging.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -883,6 +883,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes</t>
+  </si>
+  <si>
+    <t>2195: target not supported</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -5135,33 +5138,33 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5184,19 +5187,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5245,7 +5248,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5260,22 +5263,22 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5283,10 +5286,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5309,16 +5312,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5368,7 +5371,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5392,13 +5395,13 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5406,14 +5409,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5432,19 +5435,19 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5493,7 +5496,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5511,19 +5514,19 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5531,14 +5534,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5557,19 +5560,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5606,7 +5609,7 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5616,7 +5619,7 @@
         <v>169</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5625,28 +5628,28 @@
         <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5654,16 +5657,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5682,19 +5685,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5743,7 +5746,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5752,28 +5755,28 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5781,10 +5784,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5807,16 +5810,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5866,7 +5869,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5881,7 +5884,7 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
@@ -5890,13 +5893,13 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5904,10 +5907,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5930,17 +5933,17 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5989,7 +5992,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6004,22 +6007,22 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6027,10 +6030,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6053,19 +6056,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6102,7 +6105,7 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6112,7 +6115,7 @@
         <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6121,10 +6124,10 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6133,30 +6136,30 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>83</v>
@@ -6181,16 +6184,16 @@
         <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6239,7 +6242,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6248,42 +6251,42 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>83</v>
@@ -6305,19 +6308,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6366,7 +6369,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6375,42 +6378,42 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -6435,16 +6438,16 @@
         <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6493,7 +6496,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6502,39 +6505,39 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6560,16 +6563,16 @@
         <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6597,10 +6600,10 @@
         <v>187</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6618,7 +6621,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6627,13 +6630,13 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
@@ -6645,7 +6648,7 @@
         <v>136</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6656,14 +6659,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6685,16 +6688,16 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6723,7 +6726,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6741,7 +6744,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6756,33 +6759,33 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6805,19 +6808,19 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6866,7 +6869,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6881,7 +6884,7 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -6890,10 +6893,10 @@
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6904,10 +6907,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6933,13 +6936,13 @@
         <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6965,13 +6968,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6989,7 +6992,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7010,27 +7013,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7056,16 +7059,16 @@
         <v>182</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7090,13 +7093,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7114,7 +7117,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7138,10 +7141,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7152,10 +7155,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7178,16 +7181,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7237,7 +7240,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7258,27 +7261,27 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7301,16 +7304,16 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7360,7 +7363,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7381,27 +7384,27 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7424,19 +7427,19 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7485,7 +7488,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7497,7 +7500,7 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7509,10 +7512,10 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7523,10 +7526,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7644,10 +7647,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7767,14 +7770,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7796,10 +7799,10 @@
         <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>142</v>
@@ -7854,7 +7857,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7892,10 +7895,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7918,13 +7921,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7975,7 +7978,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7984,7 +7987,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7999,10 +8002,10 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8013,10 +8016,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8039,13 +8042,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8096,7 +8099,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8105,7 +8108,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -8120,10 +8123,10 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8134,10 +8137,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8163,16 +8166,16 @@
         <v>182</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8200,10 +8203,10 @@
         <v>117</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8221,7 +8224,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8242,13 +8245,13 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8259,10 +8262,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8288,16 +8291,16 @@
         <v>182</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8322,13 +8325,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8346,7 +8349,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8367,13 +8370,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8384,10 +8387,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8410,17 +8413,17 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8469,7 +8472,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8496,7 +8499,7 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8507,10 +8510,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8536,10 +8539,10 @@
         <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8590,7 +8593,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8614,10 +8617,10 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8628,10 +8631,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8654,16 +8657,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8713,7 +8716,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8737,10 +8740,10 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8751,10 +8754,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8777,16 +8780,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8836,7 +8839,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8860,10 +8863,10 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -8874,10 +8877,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8900,19 +8903,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8961,7 +8964,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8985,10 +8988,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8999,10 +9002,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9120,10 +9123,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9243,14 +9246,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9272,10 +9275,10 @@
         <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>142</v>
@@ -9330,7 +9333,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9368,10 +9371,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9397,13 +9400,13 @@
         <v>182</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>276</v>
@@ -9431,13 +9434,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9455,7 +9458,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>93</v>
@@ -9476,16 +9479,16 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -9493,10 +9496,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9519,19 +9522,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9580,7 +9583,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9601,27 +9604,27 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9647,16 +9650,16 @@
         <v>182</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9684,10 +9687,10 @@
         <v>187</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9705,7 +9708,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9714,7 +9717,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9732,7 +9735,7 @@
         <v>136</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -9743,14 +9746,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9772,16 +9775,16 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9809,28 +9812,28 @@
         <v>187</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9851,27 +9854,27 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9897,16 +9900,16 @@
         <v>84</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9955,7 +9958,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9979,10 +9982,10 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,7 +665,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1618: source value from ELECTROCARDIOGRAM (EKG) - IEN (691.5-.001)</t>
+    <t>1618: source value based on ELECTROCARDIOGRAM (EKG) - IEN (691.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -925,7 +925,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1632: reference from ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (691.5-1)</t>
+    <t>1632: reference based on ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (691.5-1)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1051,7 +1051,7 @@
 </t>
   </si>
   <si>
-    <t>1635: source value from ELECTROCARDIOGRAM (EKG) - DATE/TIME (691.5-.01)</t>
+    <t>1635: source value based on ELECTROCARDIOGRAM (EKG) - DATE/TIME (691.5-.01)</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1070,7 +1070,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1638: source value from ELECTROCARDIOGRAM (EKG) - DATE OF VERIFIED (691.5-1508)</t>
+    <t>1638: source value based on ELECTROCARDIOGRAM (EKG) - DATE OF VERIFIED (691.5-1508)</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1098,7 +1098,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1641: reference from ELECTROCARDIOGRAM (EKG) - INTERPRETED BY (691.5-12)</t>
+    <t>1641: reference based on ELECTROCARDIOGRAM (EKG) - INTERPRETED BY (691.5-12)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1158,7 +1158,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1646: source value from ELECTROCARDIOGRAM (EKG) - INTERPRETATION CODE (PACING) &gt; INTERPRETATION CODE (PACING) - INTERPRETATION CODE (PACING) &gt; ECG INTERPRETATION - INTERPRETATION (691.5-14.2 &gt; 691.56-.01 &gt; 693.3-.01)</t>
+    <t>1646: source value based on ELECTROCARDIOGRAM (EKG) - INTERPRETATION CODE (PACING) &gt; INTERPRETATION CODE (PACING) - INTERPRETATION CODE (PACING) &gt; ECG INTERPRETATION - INTERPRETATION (691.5-14.2 &gt; 691.56-.01 &gt; 693.3-.01)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>
@@ -1271,7 +1271,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1651: source value from ELECTROCARDIOGRAM (EKG) - COMMENT (691.5-17)</t>
+    <t>1651: source value based on ELECTROCARDIOGRAM (EKG) - COMMENT (691.5-17)</t>
   </si>
   <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
@@ -2061,7 +2061,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="226.4765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="230.5703125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="541">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -792,6 +792,9 @@
   </si>
   <si>
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_ImageStatus](ConceptMap-VF-ImageStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/ImageStatus</t>
@@ -1232,6 +1235,9 @@
   </si>
   <si>
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_ImageInterpretation](ConceptMap-VF-ImageInterpretation.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/ImageInterpretation</t>
@@ -4730,9 +4736,11 @@
       <c r="X22" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -4765,22 +4773,22 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -4788,10 +4796,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4817,16 +4825,16 @@
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4836,7 +4844,7 @@
         <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>83</v>
@@ -4854,16 +4862,16 @@
         <v>117</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4873,7 +4881,7 @@
         <v>169</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4888,7 +4896,7 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
@@ -4900,10 +4908,10 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4911,13 +4919,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -4942,16 +4950,16 @@
         <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4961,7 +4969,7 @@
         <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>83</v>
@@ -4979,10 +4987,10 @@
         <v>117</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5000,7 +5008,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5027,10 +5035,10 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5038,14 +5046,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5067,16 +5075,16 @@
         <v>182</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5105,7 +5113,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5123,7 +5131,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>93</v>
@@ -5138,33 +5146,33 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5187,19 +5195,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5248,7 +5256,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5263,22 +5271,22 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5286,10 +5294,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5312,16 +5320,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5371,7 +5379,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5395,13 +5403,13 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5409,14 +5417,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5435,19 +5443,19 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5496,7 +5504,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5514,19 +5522,19 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5534,14 +5542,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5560,19 +5568,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5609,7 +5617,7 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5619,7 +5627,7 @@
         <v>169</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5628,28 +5636,28 @@
         <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5657,16 +5665,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5685,19 +5693,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5746,7 +5754,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5755,28 +5763,28 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -5784,10 +5792,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5810,16 +5818,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5869,7 +5877,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5884,7 +5892,7 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
@@ -5893,13 +5901,13 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -5907,10 +5915,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5933,17 +5941,17 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5992,7 +6000,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6007,22 +6015,22 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6030,10 +6038,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6056,19 +6064,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6105,7 +6113,7 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6115,7 +6123,7 @@
         <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6124,10 +6132,10 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6136,30 +6144,30 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>83</v>
@@ -6184,16 +6192,16 @@
         <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6242,7 +6250,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6251,42 +6259,42 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>83</v>
@@ -6308,19 +6316,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6369,7 +6377,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6378,42 +6386,42 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -6438,16 +6446,16 @@
         <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6496,7 +6504,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6505,39 +6513,39 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6563,16 +6571,16 @@
         <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6600,10 +6608,10 @@
         <v>187</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6621,7 +6629,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6630,13 +6638,13 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
@@ -6648,7 +6656,7 @@
         <v>136</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6659,14 +6667,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6688,16 +6696,16 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6724,9 +6732,11 @@
       <c r="X38" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y38" s="2"/>
+      <c r="Y38" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6744,7 +6754,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6759,33 +6769,33 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6808,19 +6818,19 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6869,7 +6879,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6884,7 +6894,7 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -6893,10 +6903,10 @@
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6907,10 +6917,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6936,13 +6946,13 @@
         <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6968,13 +6978,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6992,7 +7002,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7013,27 +7023,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7059,16 +7069,16 @@
         <v>182</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7093,13 +7103,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7117,7 +7127,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7141,10 +7151,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7155,10 +7165,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7181,16 +7191,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7240,7 +7250,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7261,27 +7271,27 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7304,16 +7314,16 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7363,7 +7373,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7384,27 +7394,27 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7427,19 +7437,19 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7488,7 +7498,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7500,7 +7510,7 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7512,10 +7522,10 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7526,10 +7536,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7647,10 +7657,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7770,14 +7780,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7799,10 +7809,10 @@
         <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>142</v>
@@ -7857,7 +7867,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7895,10 +7905,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7921,13 +7931,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7978,7 +7988,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7987,7 +7997,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -8002,10 +8012,10 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8016,10 +8026,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8042,13 +8052,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8099,7 +8109,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8108,7 +8118,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -8123,10 +8133,10 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8137,10 +8147,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8166,16 +8176,16 @@
         <v>182</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8203,10 +8213,10 @@
         <v>117</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8224,7 +8234,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8245,13 +8255,13 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8262,10 +8272,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8291,16 +8301,16 @@
         <v>182</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8325,13 +8335,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8349,7 +8359,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8370,13 +8380,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8387,10 +8397,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8413,17 +8423,17 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8472,7 +8482,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8499,7 +8509,7 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8510,10 +8520,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8539,10 +8549,10 @@
         <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8593,7 +8603,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8617,10 +8627,10 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8631,10 +8641,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8657,16 +8667,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8716,7 +8726,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8740,10 +8750,10 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8754,10 +8764,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8780,16 +8790,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8839,7 +8849,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8863,10 +8873,10 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -8877,10 +8887,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8903,19 +8913,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8964,7 +8974,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8988,10 +8998,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9002,10 +9012,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9123,10 +9133,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9246,14 +9256,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9275,10 +9285,10 @@
         <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>142</v>
@@ -9333,7 +9343,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9371,10 +9381,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9400,16 +9410,16 @@
         <v>182</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9434,13 +9444,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9458,7 +9468,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>93</v>
@@ -9479,16 +9489,16 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -9496,10 +9506,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9522,19 +9532,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9583,7 +9593,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9604,27 +9614,27 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9650,16 +9660,16 @@
         <v>182</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9687,10 +9697,10 @@
         <v>187</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9708,7 +9718,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9717,7 +9727,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9735,7 +9745,7 @@
         <v>136</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
@@ -9746,14 +9756,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9775,16 +9785,16 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9812,28 +9822,28 @@
         <v>187</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Z63" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9854,27 +9864,27 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9900,16 +9910,16 @@
         <v>84</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9958,7 +9968,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9982,10 +9992,10 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -831,6 +831,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -841,29 +863,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -912,7 +912,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1162,28 +1162,6 @@
   </si>
   <si>
     <t>1646: source value based on ELECTROCARDIOGRAM (EKG) - INTERPRETATION CODE (PACING) &gt; INTERPRETATION CODE (PACING) - INTERPRETATION CODE (PACING) &gt; ECG INTERPRETATION - INTERPRETATION (691.5-14.2 &gt; 691.56-.01 &gt; 693.3-.01)</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>1797: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>1798: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2029,12 +2007,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ64"/>
+  <dimension ref="A1:AQ62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -4844,7 +4822,7 @@
         <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>263</v>
+        <v>83</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>83</v>
@@ -4862,16 +4840,16 @@
         <v>117</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4896,22 +4874,22 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -4919,13 +4897,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -4969,7 +4947,7 @@
         <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>83</v>
@@ -4987,10 +4965,10 @@
         <v>117</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5023,7 +5001,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>83</v>
@@ -5035,10 +5013,10 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -6291,11 +6269,9 @@
         <v>366</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6313,22 +6289,22 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="N35" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6353,13 +6329,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6377,7 +6353,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6386,52 +6362,50 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>360</v>
+        <v>136</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>94</v>
@@ -6440,22 +6414,22 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6480,13 +6454,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6504,48 +6478,48 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6556,7 +6530,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>94</v>
@@ -6568,19 +6542,19 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6605,13 +6579,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6629,22 +6603,22 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
@@ -6653,10 +6627,10 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>136</v>
+        <v>396</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6667,24 +6641,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>83</v>
@@ -6696,17 +6670,15 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6730,13 +6702,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>176</v>
+        <v>402</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6754,13 +6726,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6769,33 +6741,33 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6806,10 +6778,10 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -6818,19 +6790,19 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>397</v>
+        <v>182</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6855,13 +6827,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6879,13 +6851,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -6894,7 +6866,7 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -6903,10 +6875,10 @@
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6917,10 +6889,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6943,16 +6915,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>419</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6978,13 +6950,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7002,7 +6974,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7023,27 +6995,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7066,20 +7038,18 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>182</v>
+        <v>428</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -7103,13 +7073,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>421</v>
+        <v>83</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7127,7 +7097,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7148,27 +7118,27 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>432</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>83</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7179,7 +7149,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -7191,18 +7161,20 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7250,19 +7222,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>442</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7271,27 +7243,27 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7314,17 +7286,15 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>435</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>436</v>
+        <v>161</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7373,7 +7343,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>434</v>
+        <v>163</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7385,7 +7355,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7394,31 +7364,31 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>439</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>440</v>
+        <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>441</v>
+        <v>164</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7437,20 +7407,18 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>444</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>446</v>
+        <v>166</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7498,7 +7466,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>443</v>
+        <v>170</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7510,7 +7478,7 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>449</v>
+        <v>144</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7522,10 +7490,10 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>451</v>
+        <v>164</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7536,42 +7504,46 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>161</v>
+        <v>449</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7619,19 +7591,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>163</v>
+        <v>451</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7646,7 +7618,7 @@
         <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7657,21 +7629,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>83</v>
@@ -7683,17 +7655,15 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>453</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>140</v>
+        <v>454</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7742,19 +7712,19 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>456</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7766,10 +7736,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>164</v>
+        <v>458</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7780,46 +7750,42 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>455</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7867,19 +7833,19 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>456</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
@@ -7891,10 +7857,10 @@
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>136</v>
+        <v>462</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7905,10 +7871,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7931,16 +7897,20 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7964,13 +7934,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7988,7 +7958,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7997,7 +7967,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>463</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -8009,13 +7979,13 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>465</v>
+        <v>387</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8026,10 +7996,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8040,7 +8010,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -8052,16 +8022,20 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>182</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -8085,13 +8059,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>477</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>478</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8109,16 +8083,16 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>463</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -8130,13 +8104,13 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>469</v>
+        <v>387</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8147,10 +8121,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8173,19 +8147,17 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>182</v>
+        <v>480</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8210,13 +8182,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>475</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8234,7 +8206,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8255,13 +8227,13 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>477</v>
+        <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>394</v>
+        <v>484</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8272,10 +8244,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8286,7 +8258,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8298,20 +8270,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8335,37 +8303,37 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8380,13 +8348,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>477</v>
+        <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>394</v>
+        <v>488</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8397,10 +8365,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8411,7 +8379,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8420,21 +8388,21 @@
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8482,13 +8450,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8506,10 +8474,10 @@
         <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8520,10 +8488,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8534,7 +8502,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8543,18 +8511,20 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>160</v>
+        <v>497</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8603,13 +8573,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8627,10 +8597,10 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8641,10 +8611,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8667,18 +8637,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8726,7 +8698,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8750,10 +8722,10 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8764,10 +8736,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8778,7 +8750,7 @@
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>83</v>
@@ -8787,20 +8759,18 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>504</v>
+        <v>160</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>505</v>
+        <v>161</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8849,19 +8819,19 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>503</v>
+        <v>163</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8873,10 +8843,10 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>501</v>
+        <v>83</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -8887,14 +8857,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8910,23 +8880,21 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>444</v>
+        <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>510</v>
+        <v>140</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>511</v>
+        <v>166</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8974,7 +8942,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>509</v>
+        <v>170</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8986,7 +8954,7 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8998,10 +8966,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>515</v>
+        <v>164</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9012,42 +8980,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>161</v>
+        <v>449</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -9095,19 +9067,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>163</v>
+        <v>451</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -9122,7 +9094,7 @@
         <v>83</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9133,21 +9105,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -9156,21 +9128,23 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>140</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>166</v>
+        <v>514</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -9194,13 +9168,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9218,19 +9192,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>170</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -9239,16 +9213,16 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>83</v>
+        <v>518</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9256,45 +9230,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>455</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>352</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>520</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
+        <v>354</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>142</v>
+        <v>521</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>148</v>
+        <v>356</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9343,19 +9317,19 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>519</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9364,27 +9338,27 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>83</v>
+        <v>522</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>136</v>
+        <v>361</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9392,7 +9366,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
@@ -9404,22 +9378,22 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>182</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>277</v>
+        <v>370</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9444,40 +9418,40 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>409</v>
+        <v>187</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="AG60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9489,16 +9463,16 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>282</v>
+        <v>136</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>283</v>
+        <v>375</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -9506,21 +9480,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9529,22 +9503,22 @@
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>352</v>
+        <v>182</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>527</v>
+        <v>378</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>528</v>
+        <v>380</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9569,13 +9543,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9593,13 +9567,13 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>83</v>
@@ -9614,27 +9588,27 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>529</v>
+        <v>385</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9645,7 +9619,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9657,19 +9631,19 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>533</v>
+        <v>440</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>377</v>
+        <v>441</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9694,13 +9668,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9718,16 +9692,16 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9742,270 +9716,20 @@
         <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>136</v>
+        <v>443</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>382</v>
+        <v>444</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ64">
+  <autoFilter ref="A1:AQ62">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10015,7 +9739,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -928,7 +928,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1632: reference based on ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT (691.5-1)</t>
+    <t>1632: reference based on ELECTROCARDIOGRAM (EKG) - MEDICAL PATIENT &gt; MEDICAL PATIENT - NAME (691.5-1 &gt; 690-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultEKG.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
